--- a/artfynd/A 9944-2026 artfynd.xlsx
+++ b/artfynd/A 9944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136004654</v>
       </c>
       <c r="B2" t="n">
-        <v>90830</v>
+        <v>90832</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136004505</v>
       </c>
       <c r="B3" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9944-2026 artfynd.xlsx
+++ b/artfynd/A 9944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136004654</v>
       </c>
       <c r="B2" t="n">
-        <v>90832</v>
+        <v>90833</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9944-2026 artfynd.xlsx
+++ b/artfynd/A 9944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136004654</v>
       </c>
       <c r="B2" t="n">
-        <v>90833</v>
+        <v>90834</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9944-2026 artfynd.xlsx
+++ b/artfynd/A 9944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136004654</v>
       </c>
       <c r="B2" t="n">
-        <v>90834</v>
+        <v>90835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136004505</v>
       </c>
       <c r="B3" t="n">
-        <v>58086</v>
+        <v>58087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9944-2026 artfynd.xlsx
+++ b/artfynd/A 9944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136004654</v>
       </c>
       <c r="B2" t="n">
-        <v>90835</v>
+        <v>90841</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136004505</v>
       </c>
       <c r="B3" t="n">
-        <v>58087</v>
+        <v>58091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9944-2026 artfynd.xlsx
+++ b/artfynd/A 9944-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136004654</v>
       </c>
       <c r="B2" t="n">
-        <v>90841</v>
+        <v>90842</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         <v>136004505</v>
       </c>
       <c r="B3" t="n">
-        <v>58091</v>
+        <v>58092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
